--- a/static/standards-correlations/Colorado_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Colorado_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$32</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Adopted May 9 2024, implementation 2026-27 - COMPLETE, 28 GLEs</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Adopted May 9 2024, implementation 2026-27 - COMPLETE, 28 GLEs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1309,7 +1310,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Ext 1.1F (Why a PIN?) covers authentication weakness, Ext 5.3G (Secret Messages / HTTPS) covers interception in transit, and Discovery Systems 10 covers phishing as a threat to the person. Penetration testing and intrusion process are absent.</t>
+          <t>Ext 1.1F (Why a PIN?) covers authentication weakness, Ext 5.3G (Secret Messages / HTTPS) covers interception in transit, and Introductory Systems 10 covers phishing as a threat to the person. Penetration testing and intrusion process are absent.</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1357,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Identifying constraints, planning with flowcharts, choosing a text-based language, and applying core programming concepts are all covered. Discovery Systems 5 teaches the design cycle explicitly.</t>
+          <t>Identifying constraints, planning with flowcharts, choosing a text-based language, and applying core programming concepts are all covered. Introductory Systems 5 teaches the design cycle explicitly.</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1729,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers phishing and why emotional pressure works, which is adversarial thinking about social engineering. Ext 1.1F (Why a PIN?) asks what an attacker gains from a weak PIN. Risk profiles are not built.</t>
+          <t>Introductory Systems 10 covers phishing and why emotional pressure works, which is adversarial thinking about social engineering. Ext 1.1F (Why a PIN?) asks what an attacker gains from a weak PIN. Risk profiles are not built.</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1889,7 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>The strongest row in Standard 5, and the one place this curriculum's AI work maps onto Colorado's strand without strain. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Those prompts are core, not optional, and they pose the dilemma as an unresolved one - Discovery Systems 12 asks whose responsibility it is to anticipate harm when something genuinely useful also causes it. Ext 5.2D (Should It Exist?) requires students to research a real incident involving a deployed system and take a defended position on whether it should exist. Ext 2.6E (Automatic Data Collection) raises continuous automatic collection that nobody individually approves, and Ext 5.3D (Who's Left Out?) raises who is excluded by design assumptions. On the legal half, Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. establishes intellectual property and licensing as real constraints, though not AI-specific ones.</t>
+          <t>The strongest row in Standard 5, and the one place this curriculum's AI work maps onto Colorado's strand without strain. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Those prompts are core, not optional, and they pose the dilemma as an unresolved one - Introductory Systems 12 asks whose responsibility it is to anticipate harm when something genuinely useful also causes it. Ext 5.2D (Should It Exist?) requires students to research a real incident involving a deployed system and take a defended position on whether it should exist. Ext 2.6E (Automatic Data Collection) raises continuous automatic collection that nobody individually approves, and Ext 5.3D (Who's Left Out?) raises who is excluded by design assumptions. On the legal half, Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. establishes intellectual property and licensing as real constraints, though not AI-specific ones.</t>
         </is>
       </c>
     </row>
@@ -1922,6 +1923,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1966,7 +1968,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1980,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2126,6 +2128,8 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
@@ -2156,7 +2160,7 @@
 UNIT OF ANALYSIS: Colorado organizes content as Grade Level Expectations with Evidence Outcomes beneath each. This crosswalk maps at the GLE level; coverage judgments consider the Evidence Outcomes but do not list them as separate rows.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT: 21 Full, 6 Partial, 1 blank of 28.
   Standard 1 Computational Thinking      8 GLEs
